--- a/samples/s11_单位名脏格式.xlsx
+++ b/samples/s11_单位名脏格式.xlsx
@@ -418,7 +418,7 @@
         <v>2026-08-05</v>
       </c>
       <c r="B2" t="str">
-        <v xml:space="preserve">  邯郸市甲辰建材有限公司  </v>
+        <v xml:space="preserve">  某市甲辰建材有限公司  </v>
       </c>
       <c r="C2" t="str">
         <v>销售开票</v>
@@ -432,7 +432,7 @@
         <v>2026-08-06</v>
       </c>
       <c r="B3" t="str">
-        <v>邯郸市甲辰建材有限公司</v>
+        <v>某市甲辰建材有限公司</v>
       </c>
       <c r="C3" t="str">
         <v>销售开票</v>
@@ -446,7 +446,7 @@
         <v>2026-08-07</v>
       </c>
       <c r="B4" t="str">
-        <v>邯郸市丙通物流有限公司</v>
+        <v>某市丙通物流有限公司</v>
       </c>
       <c r="C4" t="str">
         <v>运输服务</v>
